--- a/Test_Cases_Gaps.xlsx
+++ b/Test_Cases_Gaps.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Gap Test Cases" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Gap Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gap Test Cases'!$A$1:$K$182</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -71,7 +73,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -85,11 +87,25 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -115,6 +131,13 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:K182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5740,7 +5763,5138 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t>X-01</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>Leagues - Ladder</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>confirmChallenge is atomic under concurrent confirms</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F93" s="11" t="inlineStr">
+        <is>
+          <t>/matches</t>
+        </is>
+      </c>
+      <c r="G93" s="11" t="inlineStr">
+        <is>
+          <t>A reported challenge; loser has leaguePoints26 = 10</t>
+        </is>
+      </c>
+      <c r="H93" s="11" t="inlineStr">
+        <is>
+          <t>1. Two organizers open the same reported challenge. 2. Both click Confirm at the same time.</t>
+        </is>
+      </c>
+      <c r="I93" s="11" t="inlineStr">
+        <is>
+          <t>Loser loses exactly one 3-point deduction per confirm that actually applies; no deduction is silently lost. Was a read-modify-absolute-write in a batch.</t>
+        </is>
+      </c>
+      <c r="J93" s="11" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K93" s="11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="11" t="inlineStr">
+        <is>
+          <t>X-02</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>Leagues - Ladder</t>
+        </is>
+      </c>
+      <c r="C94" s="11" t="inlineStr">
+        <is>
+          <t>confirmChallenge with a missing stats doc</t>
+        </is>
+      </c>
+      <c r="D94" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E94" s="11" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F94" s="11" t="inlineStr">
+        <is>
+          <t>/matches</t>
+        </is>
+      </c>
+      <c r="G94" s="11" t="inlineStr">
+        <is>
+          <t>One player has no stats/{uid} document</t>
+        </is>
+      </c>
+      <c r="H94" s="11" t="inlineStr">
+        <is>
+          <t>1. Report a challenge involving that player. 2. Confirm it.</t>
+        </is>
+      </c>
+      <c r="I94" s="11" t="inlineStr">
+        <is>
+          <t>Confirm succeeds and the stats doc is created via set(merge). Previously batch.update rejected the whole batch and stranded the challenge in reported.</t>
+        </is>
+      </c>
+      <c r="J94" s="11" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K94" s="11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="11" t="inlineStr">
+        <is>
+          <t>X-03</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>Tournament - Scores</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr">
+        <is>
+          <t>RR draw reset does not deduct an unpaid group bonus</t>
+        </is>
+      </c>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F95" s="11" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G95" s="11" t="inlineStr">
+        <is>
+          <t>An RR group whose matches are all complete but whose +5 bonus commit failed (no rr_group_bonus_v2 stamp)</t>
+        </is>
+      </c>
+      <c r="H95" s="11" t="inlineStr">
+        <is>
+          <t>1. Complete every match in a group. 2. Simulate/force the bonus commit failing. 3. Cancel the draw.</t>
+        </is>
+      </c>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>No -5 is applied to those players. Reversal only runs when the rr_group_bonus_v2 stamp is present.</t>
+        </is>
+      </c>
+      <c r="J95" s="11" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K95" s="11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
+          <t>X-04</t>
+        </is>
+      </c>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t>Tournament - Scores</t>
+        </is>
+      </c>
+      <c r="C96" s="11" t="inlineStr">
+        <is>
+          <t>RR draw reset DOES reverse a paid group bonus</t>
+        </is>
+      </c>
+      <c r="D96" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E96" s="11" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F96" s="11" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G96" s="11" t="inlineStr">
+        <is>
+          <t>An RR group fully played with the +5 bonus paid and stamped</t>
+        </is>
+      </c>
+      <c r="H96" s="11" t="inlineStr">
+        <is>
+          <t>1. Complete every match in a group (bonus pays). 2. Cancel the draw.</t>
+        </is>
+      </c>
+      <c r="I96" s="11" t="inlineStr">
+        <is>
+          <t>Each player in that group loses exactly 5 leaguePoints26 — the stamp guard must not suppress legitimate reversals.</t>
+        </is>
+      </c>
+      <c r="J96" s="11" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K96" s="11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t>X-05</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>Tournament - Draw</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>RR draft follows the selected zone</t>
+        </is>
+      </c>
+      <c r="D97" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F97" s="11" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G97" s="11" t="inlineStr">
+        <is>
+          <t>A zone-enabled RR event with saved group drafts in two different zones</t>
+        </is>
+      </c>
+      <c r="H97" s="11" t="inlineStr">
+        <is>
+          <t>1. Arrange groups in zone A. 2. Switch the zone selector to zone B.</t>
+        </is>
+      </c>
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>The preview shows zone B's draft, not zone A's. Saving writes zone B's roster. The rr_drafts subscription keys on currentDrawKey (which includes zone).</t>
+        </is>
+      </c>
+      <c r="J97" s="11" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K97" s="11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t>X-06</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>Tournament - Draw</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>Participant lands on their own zone draw</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="F98" s="11" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G98" s="11" t="inlineStr">
+        <is>
+          <t>A zone-enabled event; participant has a preferred zone; draw not yet generated</t>
+        </is>
+      </c>
+      <c r="H98" s="11" t="inlineStr">
+        <is>
+          <t>1. Open the tournament page as that participant (cold load).</t>
+        </is>
+      </c>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>Active zone resolves to the participant's own zone once preferences load. Previously zoneMap was a stale {} and the fallback never re-ran.</t>
+        </is>
+      </c>
+      <c r="J98" s="11" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="K98" s="11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>X-07</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>Tournament - Draw</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>Pre-generation draw visibility (intended behaviour)</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G99" s="11" t="inlineStr">
+        <is>
+          <t>Participant registered, no draw generated yet</t>
+        </is>
+      </c>
+      <c r="H99" s="11" t="inlineStr">
+        <is>
+          <t>1. Open the tournament page.</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>All draws are visible and userDraw is undefined. This is intentional — do NOT add a skill-derived fallback.</t>
+        </is>
+      </c>
+      <c r="J99" s="11" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="K99" s="11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t>X-08</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>Leagues</t>
+        </is>
+      </c>
+      <c r="C100" s="11" t="inlineStr">
+        <is>
+          <t>Completed match with no winner does not eliminate player 1</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>/leagues</t>
+        </is>
+      </c>
+      <c r="G100" s="11" t="inlineStr">
+        <is>
+          <t>A tournament_matches doc with status=complete and no winner_user_id</t>
+        </is>
+      </c>
+      <c r="H100" s="11" t="inlineStr">
+        <is>
+          <t>1. Load /leagues with such a match present.</t>
+        </is>
+      </c>
+      <c r="I100" s="11" t="inlineStr">
+        <is>
+          <t>Neither player is marked eliminated; player 1 still shows as active. Previously undefined !== player_1 made player 1 the loser.</t>
+        </is>
+      </c>
+      <c r="J100" s="11" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K100" s="11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>X-09</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>Sign-out clears upcoming matches</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="F101" s="11" t="inlineStr">
+        <is>
+          <t>/profile</t>
+        </is>
+      </c>
+      <c r="G101" s="11" t="inlineStr">
+        <is>
+          <t>Signed-in user with upcoming matches rendered</t>
+        </is>
+      </c>
+      <c r="H101" s="11" t="inlineStr">
+        <is>
+          <t>1. View profile/home with upcoming matches. 2. Sign out. 3. Observe before remount.</t>
+        </is>
+      </c>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>Both completed and upcoming lists clear. Previously upcoming retained the previous user's opponent names and contact strings.</t>
+        </is>
+      </c>
+      <c r="J101" s="11" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="K101" s="11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t>X-10</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C102" s="11" t="inlineStr">
+        <is>
+          <t>Google sign-in via shared useOAuthSignIn</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E102" s="11" t="inlineStr">
+        <is>
+          <t>New User</t>
+        </is>
+      </c>
+      <c r="F102" s="11" t="inlineStr">
+        <is>
+          <t>/login</t>
+        </is>
+      </c>
+      <c r="G102" s="11" t="inlineStr">
+        <is>
+          <t>Google account not yet in Firebase</t>
+        </is>
+      </c>
+      <c r="H102" s="11" t="inlineStr">
+        <is>
+          <t>1. Click Continue with Google. 2. Complete the popup.</t>
+        </is>
+      </c>
+      <c r="I102" s="11" t="inlineStr">
+        <is>
+          <t>Signs in, bootstraps profile docs, tracks sign_up, routes to /login for a new user. Behaviour identical to before the hook was shared.</t>
+        </is>
+      </c>
+      <c r="J102" s="11" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="K102" s="11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>X-11</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>Apple sign-in via shared useOAuthSignIn</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>New User</t>
+        </is>
+      </c>
+      <c r="F103" s="11" t="inlineStr">
+        <is>
+          <t>/login</t>
+        </is>
+      </c>
+      <c r="G103" s="11" t="inlineStr">
+        <is>
+          <t>Apple account not yet in Firebase</t>
+        </is>
+      </c>
+      <c r="H103" s="11" t="inlineStr">
+        <is>
+          <t>1. Click Continue with Apple. 2. Complete the popup.</t>
+        </is>
+      </c>
+      <c r="I103" s="11" t="inlineStr">
+        <is>
+          <t>Same as X-10 with method=apple. Each hook filters getRedirectResult on its own providerId, so neither consumes the other's result.</t>
+        </is>
+      </c>
+      <c r="J103" s="11" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="K103" s="11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>X-12</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C104" s="11" t="inlineStr">
+        <is>
+          <t>OAuth popup blocked falls back to redirect</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E104" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>/login</t>
+        </is>
+      </c>
+      <c r="G104" s="11" t="inlineStr">
+        <is>
+          <t>Browser blocking popups (iOS in-app browser)</t>
+        </is>
+      </c>
+      <c r="H104" s="11" t="inlineStr">
+        <is>
+          <t>1. Block popups. 2. Click Continue with Google, then repeat with Apple.</t>
+        </is>
+      </c>
+      <c r="I104" s="11" t="inlineStr">
+        <is>
+          <t>Falls back to signInWithRedirect and completes on return for both providers.</t>
+        </is>
+      </c>
+      <c r="J104" s="11" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="K104" s="11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>X-13</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>OAuth account-exists linking prompt</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>/login</t>
+        </is>
+      </c>
+      <c r="G105" s="11" t="inlineStr">
+        <is>
+          <t>Email/password account exists with the same email</t>
+        </is>
+      </c>
+      <c r="H105" s="11" t="inlineStr">
+        <is>
+          <t>1. Sign in with Google (then Apple) using that email.</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>onAccountExists fires with email + credential; the password-link prompt appears. Error copy names the right provider.</t>
+        </is>
+      </c>
+      <c r="J105" s="11" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="K105" s="11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>X-14</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>Court Map</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>Programs load from the slim prebuilt CSV</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>/courts</t>
+        </is>
+      </c>
+      <c r="G106" s="11" t="inlineStr">
+        <is>
+          <t>npm run build has produced public/programs-tennis.csv</t>
+        </is>
+      </c>
+      <c r="H106" s="11" t="inlineStr">
+        <is>
+          <t>1. Open /courts. 2. Switch to the Programs view. 3. Check the network tab.</t>
+        </is>
+      </c>
+      <c r="I106" s="11" t="inlineStr">
+        <is>
+          <t>Fetches /programs-tennis.csv (~0.15 MB), not the 9 MB source. Programs list and filters behave exactly as before.</t>
+        </is>
+      </c>
+      <c r="J106" s="11" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="K106" s="11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>X-15</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>Court Map</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>Court counts read the site_stats aggregate</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>Logged out</t>
+        </is>
+      </c>
+      <c r="F107" s="11" t="inlineStr">
+        <is>
+          <t>/courts</t>
+        </is>
+      </c>
+      <c r="G107" s="11" t="inlineStr">
+        <is>
+          <t>aggregateCourtCounts deployed and has run at least once</t>
+        </is>
+      </c>
+      <c r="H107" s="11" t="inlineStr">
+        <is>
+          <t>1. Open /courts logged out. 2. Check the network tab.</t>
+        </is>
+      </c>
+      <c r="I107" s="11" t="inlineStr">
+        <is>
+          <t>Reads one site_stats/court_counts doc. No full preferences/stats/users collection downloads. Counts match the previous numbers.</t>
+        </is>
+      </c>
+      <c r="J107" s="11" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K107" s="11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t>X-16</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>Court Map</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>Court counts fall back when the aggregate is missing</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>Logged out</t>
+        </is>
+      </c>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>/courts</t>
+        </is>
+      </c>
+      <c r="G108" s="11" t="inlineStr">
+        <is>
+          <t>site_stats/court_counts absent or empty (e.g. function not yet deployed)</t>
+        </is>
+      </c>
+      <c r="H108" s="11" t="inlineStr">
+        <is>
+          <t>1. Delete/empty the doc. 2. Open /courts.</t>
+        </is>
+      </c>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>Falls back to the original client-side computation and counts still render — no regression before deploy.</t>
+        </is>
+      </c>
+      <c r="J108" s="11" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K108" s="11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t>X-17</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>Court Map</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>Search input stays responsive with all courts shown</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="F109" s="11" t="inlineStr">
+        <is>
+          <t>/courts</t>
+        </is>
+      </c>
+      <c r="G109" s="11" t="inlineStr">
+        <is>
+          <t>No filters applied (~600 markers)</t>
+        </is>
+      </c>
+      <c r="H109" s="11" t="inlineStr">
+        <is>
+          <t>1. Type a multi-character query quickly into the search box.</t>
+        </is>
+      </c>
+      <c r="I109" s="11" t="inlineStr">
+        <is>
+          <t>No perceptible input lag. Markers and result lists are memoized so they no longer rebuild per keystroke.</t>
+        </is>
+      </c>
+      <c r="J109" s="11" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="K109" s="11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t>X-18</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="inlineStr">
+        <is>
+          <t>Court Map</t>
+        </is>
+      </c>
+      <c r="C110" s="11" t="inlineStr">
+        <is>
+          <t>Pickleball markers still render</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="F110" s="11" t="inlineStr">
+        <is>
+          <t>/courts</t>
+        </is>
+      </c>
+      <c r="G110" s="11" t="inlineStr">
+        <is>
+          <t>Pickleball-only courts present</t>
+        </is>
+      </c>
+      <c r="H110" s="11" t="inlineStr">
+        <is>
+          <t>1. Open /courts. 2. Locate a standalone pickleball marker. 3. Click it.</t>
+        </is>
+      </c>
+      <c r="I110" s="11" t="inlineStr">
+        <is>
+          <t>Marker renders identically (now via the shared soloMarkerSvg) and the popup opens.</t>
+        </is>
+      </c>
+      <c r="J110" s="11" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="K110" s="11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>X-19</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t>Leagues - Ladder</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>Rally rows do not remount on unrelated state changes</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>/matches</t>
+        </is>
+      </c>
+      <c r="G111" s="11" t="inlineStr">
+        <is>
+          <t>At least one open sent and one open received rally</t>
+        </is>
+      </c>
+      <c r="H111" s="11" t="inlineStr">
+        <is>
+          <t>1. Open Friendlies. 2. Trigger unrelated state changes (switch mode, open/close a modal).</t>
+        </is>
+      </c>
+      <c r="I111" s="11" t="inlineStr">
+        <is>
+          <t>Rally rows keep DOM state and do not replay mount animations. RallyRow is declared at module scope.</t>
+        </is>
+      </c>
+      <c r="J111" s="11" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="K111" s="11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t>X-20</t>
+        </is>
+      </c>
+      <c r="B112" s="11" t="inlineStr">
+        <is>
+          <t>Leagues - Ladder</t>
+        </is>
+      </c>
+      <c r="C112" s="11" t="inlineStr">
+        <is>
+          <t>Challenge score submission builds the same score line</t>
+        </is>
+      </c>
+      <c r="D112" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E112" s="11" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="F112" s="11" t="inlineStr">
+        <is>
+          <t>/matches</t>
+        </is>
+      </c>
+      <c r="G112" s="11" t="inlineStr">
+        <is>
+          <t>An accepted challenge ready to report</t>
+        </is>
+      </c>
+      <c r="H112" s="11" t="inlineStr">
+        <is>
+          <t>1. Report a score with a mix of filled and empty sets (e.g. 6-3, 6-4, blank).</t>
+        </is>
+      </c>
+      <c r="I112" s="11" t="inlineStr">
+        <is>
+          <t>score_line is "6-3, 6-4" — blank sets dropped. Now uses the shared buildScoreLine helper.</t>
+        </is>
+      </c>
+      <c r="J112" s="11" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="K112" s="11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>X-21</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>Tournament - Draw</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>Participant/stats load is batched, not N+1</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G113" s="11" t="inlineStr">
+        <is>
+          <t>An event with 30+ participants</t>
+        </is>
+      </c>
+      <c r="H113" s="11" t="inlineStr">
+        <is>
+          <t>1. Open the tournament page. 2. Watch Firestore reads in the network tab.</t>
+        </is>
+      </c>
+      <c r="I113" s="11" t="inlineStr">
+        <is>
+          <t>users/stats load in chunks of 10 via documentId() in — roughly ceil(N/10) queries per collection, not one per participant.</t>
+        </is>
+      </c>
+      <c r="J113" s="11" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K113" s="11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t>X-22</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>Tournament - Draw</t>
+        </is>
+      </c>
+      <c r="C114" s="11" t="inlineStr">
+        <is>
+          <t>Merged-draw toggles infer the right skill pair</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F114" s="11" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G114" s="11" t="inlineStr">
+        <is>
+          <t>A generated merged (skill_group=All) singles draw including Beginners</t>
+        </is>
+      </c>
+      <c r="H114" s="11" t="inlineStr">
+        <is>
+          <t>1. Reload the tournament page cold. 2. Inspect the merge toggle.</t>
+        </is>
+      </c>
+      <c r="I114" s="11" t="inlineStr">
+        <is>
+          <t>Infers the correct pair (e.g. Beginners+Challengers) once stats load. Previously the inference ran inside the snapshot callback with a stale empty statsMap and always fell back to Challengers+Masters.</t>
+        </is>
+      </c>
+      <c r="J114" s="11" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K114" s="11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t>X-23</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
+          <t>map-vendor chunk is emitted</t>
+        </is>
+      </c>
+      <c r="D115" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F115" s="11" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="G115" s="11" t="inlineStr">
+        <is>
+          <t>Clean working tree</t>
+        </is>
+      </c>
+      <c r="H115" s="11" t="inlineStr">
+        <is>
+          <t>1. Run npm run build. 2. Inspect dist/assets.</t>
+        </is>
+      </c>
+      <c r="I115" s="11" t="inlineStr">
+        <is>
+          <t>A separate map-vendor chunk exists containing maplibre-gl/react-map-gl, so it caches across deploys.</t>
+        </is>
+      </c>
+      <c r="J115" s="11" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="K115" s="11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>X-24</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="inlineStr">
+        <is>
+          <t>Source programs CSV is not deployed</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F116" s="11" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="G116" s="11" t="inlineStr">
+        <is>
+          <t>Clean working tree</t>
+        </is>
+      </c>
+      <c r="H116" s="11" t="inlineStr">
+        <is>
+          <t>1. Run npm run build. 2. List dist/.</t>
+        </is>
+      </c>
+      <c r="I116" s="11" t="inlineStr">
+        <is>
+          <t>dist/ contains programs-tennis.csv but NOT the 9 MB Registered Programs.csv (it lives in data/, outside public/).</t>
+        </is>
+      </c>
+      <c r="J116" s="11" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="K116" s="11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="12" t="inlineStr">
+        <is>
+          <t>Z-01</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="inlineStr">
+        <is>
+          <t>Zones</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>Pre-zone groups map onto the default zone</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="inlineStr">
+        <is>
+          <t>Participant</t>
+        </is>
+      </c>
+      <c r="F117" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G117" s="12" t="inlineStr">
+        <is>
+          <t>RR draw with groups generated before zones went live (no zone field)</t>
+        </is>
+      </c>
+      <c r="H117" s="12" t="inlineStr">
+        <is>
+          <t>1. Open the event. 2. Count draws and signups.</t>
+        </is>
+      </c>
+      <c r="I117" s="12" t="inlineStr">
+        <is>
+          <t>Zone-less groups appear under Downtown-Midtown (effectiveZone), NOT as a separate fourth zone. No participant matches two draws; signup counts are not doubled.</t>
+        </is>
+      </c>
+      <c r="J117" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K117" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="12" t="inlineStr">
+        <is>
+          <t>Z-02</t>
+        </is>
+      </c>
+      <c r="B118" s="12" t="inlineStr">
+        <is>
+          <t>Zones</t>
+        </is>
+      </c>
+      <c r="C118" s="12" t="inlineStr">
+        <is>
+          <t>Resetting one zone draw leaves the other zone intact</t>
+        </is>
+      </c>
+      <c r="D118" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E118" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F118" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G118" s="12" t="inlineStr">
+        <is>
+          <t>Two zone draws in the SAME division/skill, both generated, no scores</t>
+        </is>
+      </c>
+      <c r="H118" s="12" t="inlineStr">
+        <is>
+          <t>1. Reset the North York draw. 2. Inspect the other zone's matches and players' leaguePoints26.</t>
+        </is>
+      </c>
+      <c r="I118" s="12" t="inlineStr">
+        <is>
+          <t>Only North York match docs are deleted. The other zone's matches and points are untouched (currentMatches filters on zone).</t>
+        </is>
+      </c>
+      <c r="J118" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K118" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="12" t="inlineStr">
+        <is>
+          <t>Z-03</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>Zones</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>Cancel/regenerate is zone-scoped</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F119" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G119" s="12" t="inlineStr">
+        <is>
+          <t>Same as Z-02</t>
+        </is>
+      </c>
+      <c r="H119" s="12" t="inlineStr">
+        <is>
+          <t>1. Cancel and regenerate one zone draw.</t>
+        </is>
+      </c>
+      <c r="I119" s="12" t="inlineStr">
+        <is>
+          <t>Only that zone's docs are rewritten; the sibling zone draw is byte-identical before/after.</t>
+        </is>
+      </c>
+      <c r="J119" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K119" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="12" t="inlineStr">
+        <is>
+          <t>Z-04</t>
+        </is>
+      </c>
+      <c r="B120" s="12" t="inlineStr">
+        <is>
+          <t>Zones</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>Winner advancement stays inside its zone</t>
+        </is>
+      </c>
+      <c r="D120" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E120" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F120" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G120" s="12" t="inlineStr">
+        <is>
+          <t>Two zone draws where template match ids (M1, M5...) repeat across zones</t>
+        </is>
+      </c>
+      <c r="H120" s="12" t="inlineStr">
+        <is>
+          <t>1. Score a match in zone A whose winner advances. 2. Inspect the same-numbered match in zone B.</t>
+        </is>
+      </c>
+      <c r="I120" s="12" t="inlineStr">
+        <is>
+          <t>Winner lands in the next match of the SAME zone. Zone B's same-id match is untouched (advancement normalizes zone + bracket, not just match id).</t>
+        </is>
+      </c>
+      <c r="J120" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K120" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="12" t="inlineStr">
+        <is>
+          <t>Z-05</t>
+        </is>
+      </c>
+      <c r="B121" s="12" t="inlineStr">
+        <is>
+          <t>Zones</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>Participant zone-change request</t>
+        </is>
+      </c>
+      <c r="D121" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>Participant</t>
+        </is>
+      </c>
+      <c r="F121" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G121" s="12" t="inlineStr">
+        <is>
+          <t>Signed-in participant in a zone draw</t>
+        </is>
+      </c>
+      <c r="H121" s="12" t="inlineStr">
+        <is>
+          <t>1. Request a zone change. 2. Check Firestore + creator's feed.</t>
+        </is>
+      </c>
+      <c r="I121" s="12" t="inlineStr">
+        <is>
+          <t>event_participants updates only zone_change_requested / zone_change_requested_at (rules whitelist). onZoneChangeRequested notifies the creator.</t>
+        </is>
+      </c>
+      <c r="J121" s="12" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="K121" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="12" t="inlineStr">
+        <is>
+          <t>Z-06</t>
+        </is>
+      </c>
+      <c r="B122" s="12" t="inlineStr">
+        <is>
+          <t>Zones</t>
+        </is>
+      </c>
+      <c r="C122" s="12" t="inlineStr">
+        <is>
+          <t>Boundary courts resolve to exactly one zone</t>
+        </is>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F122" s="12" t="inlineStr">
+        <is>
+          <t>/courts</t>
+        </is>
+      </c>
+      <c r="G122" s="12" t="inlineStr">
+        <is>
+          <t>Courts near the DVP/Hwy 404 corridor and the east-edge chain</t>
+        </is>
+      </c>
+      <c r="H122" s="12" t="inlineStr">
+        <is>
+          <t>1. Resolve zone for boundary courts (unit-test zones.ts).</t>
+        </is>
+      </c>
+      <c r="I122" s="12" t="inlineStr">
+        <is>
+          <t>Each court falls in exactly one zone - no overlap wedge (DVP+404 are spliced as one polyline; east edge re-binned at ~300m).</t>
+        </is>
+      </c>
+      <c r="J122" s="12" t="inlineStr">
+        <is>
+          <t>Automated unit</t>
+        </is>
+      </c>
+      <c r="K122" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="12" t="inlineStr">
+        <is>
+          <t>Z-07</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>Zones</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>Group labels drop the zone segment when mixed/unassigned</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F123" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G123" s="12" t="inlineStr">
+        <is>
+          <t>RR groups from mixed zones and from one zone</t>
+        </is>
+      </c>
+      <c r="H123" s="12" t="inlineStr">
+        <is>
+          <t>1. Inspect group labels.</t>
+        </is>
+      </c>
+      <c r="I123" s="12" t="inlineStr">
+        <is>
+          <t>Single-zone group: 'Group X · Band · Zone'. Mixed/unassigned: zone segment dropped. Creator-renamed label (rr_label_custom) shown verbatim.</t>
+        </is>
+      </c>
+      <c r="J123" s="12" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="K123" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="12" t="inlineStr">
+        <is>
+          <t>Z-08</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="inlineStr">
+        <is>
+          <t>Zones</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>Zone court counts</t>
+        </is>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="F124" s="12" t="inlineStr">
+        <is>
+          <t>/courts</t>
+        </is>
+      </c>
+      <c r="G124" s="12" t="inlineStr">
+        <is>
+          <t>zoneCourtCounts data present</t>
+        </is>
+      </c>
+      <c r="H124" s="12" t="inlineStr">
+        <is>
+          <t>1. Open the court map zone view.</t>
+        </is>
+      </c>
+      <c r="I124" s="12" t="inlineStr">
+        <is>
+          <t>Per-zone court counts match the zones.ts assignment of the courts CSV.</t>
+        </is>
+      </c>
+      <c r="J124" s="12" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="K124" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="12" t="inlineStr">
+        <is>
+          <t>RR-01</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>Round Robin</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>splitEvenly group sizes</t>
+        </is>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F125" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G125" s="12" t="inlineStr">
+        <is>
+          <t>RR draws with 6, 7, 9, 11, 12 same-band/zone players</t>
+        </is>
+      </c>
+      <c r="H125" s="12" t="inlineStr">
+        <is>
+          <t>1. Preview each draw. 2. Note group sizes.</t>
+        </is>
+      </c>
+      <c r="I125" s="12" t="inlineStr">
+        <is>
+          <t>6→[3,3], 7→[4,3], 9→[5,4], 11→[4,4,3], 12→[4,4,4]. g = ceil(n/5), balanced 3-5. The size algorithm is authoritative - band boundaries never force a 3+2 split.</t>
+        </is>
+      </c>
+      <c r="J125" s="12" t="inlineStr">
+        <is>
+          <t>Automated unit</t>
+        </is>
+      </c>
+      <c r="K125" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="12" t="inlineStr">
+        <is>
+          <t>RR-02</t>
+        </is>
+      </c>
+      <c r="B126" s="12" t="inlineStr">
+        <is>
+          <t>Round Robin</t>
+        </is>
+      </c>
+      <c r="C126" s="12" t="inlineStr">
+        <is>
+          <t>≤5 total players form one group</t>
+        </is>
+      </c>
+      <c r="D126" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E126" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F126" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G126" s="12" t="inlineStr">
+        <is>
+          <t>RR draw with 5 players across different bands/zones</t>
+        </is>
+      </c>
+      <c r="H126" s="12" t="inlineStr">
+        <is>
+          <t>1. Preview the draw.</t>
+        </is>
+      </c>
+      <c r="I126" s="12" t="inlineStr">
+        <is>
+          <t>One single group - band and zone are ignored at ≤5 total.</t>
+        </is>
+      </c>
+      <c r="J126" s="12" t="inlineStr">
+        <is>
+          <t>Automated unit</t>
+        </is>
+      </c>
+      <c r="K126" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="12" t="inlineStr">
+        <is>
+          <t>RR-03</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="inlineStr">
+        <is>
+          <t>Round Robin</t>
+        </is>
+      </c>
+      <c r="C127" s="12" t="inlineStr">
+        <is>
+          <t>Lone player in a distinct zone</t>
+        </is>
+      </c>
+      <c r="D127" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F127" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G127" s="12" t="inlineStr">
+        <is>
+          <t>One band with players clustered in 3 zones + a single player in a 4th zone</t>
+        </is>
+      </c>
+      <c r="H127" s="12" t="inlineStr">
+        <is>
+          <t>1. Preview with &gt;3 zone-clustered groups. 2. Repeat with fewer groups.</t>
+        </is>
+      </c>
+      <c r="I127" s="12" t="inlineStr">
+        <is>
+          <t>With &gt;3 clustered groups the singleton gets a placeholder group; otherwise the band pools (ordered by zone) and splitEvenly folds the singleton in. Nobody is dropped.</t>
+        </is>
+      </c>
+      <c r="J127" s="12" t="inlineStr">
+        <is>
+          <t>Automated unit</t>
+        </is>
+      </c>
+      <c r="K127" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="12" t="inlineStr">
+        <is>
+          <t>RR-04</t>
+        </is>
+      </c>
+      <c r="B128" s="12" t="inlineStr">
+        <is>
+          <t>Round Robin</t>
+        </is>
+      </c>
+      <c r="C128" s="12" t="inlineStr">
+        <is>
+          <t>Preview equals generated draw</t>
+        </is>
+      </c>
+      <c r="D128" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E128" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F128" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G128" s="12" t="inlineStr">
+        <is>
+          <t>Any RR draw in preview</t>
+        </is>
+      </c>
+      <c r="H128" s="12" t="inlineStr">
+        <is>
+          <t>1. Note previewed groups. 2. Generate. 3. Compare.</t>
+        </is>
+      </c>
+      <c r="I128" s="12" t="inlineStr">
+        <is>
+          <t>Generated groups are identical to the preview (previewRRGroups uses the same buildZoneTierGroups function).</t>
+        </is>
+      </c>
+      <c r="J128" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K128" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="12" t="inlineStr">
+        <is>
+          <t>RR-05</t>
+        </is>
+      </c>
+      <c r="B129" s="12" t="inlineStr">
+        <is>
+          <t>Round Robin</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="inlineStr">
+        <is>
+          <t>Group letters are positional after rename/dissolve</t>
+        </is>
+      </c>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F129" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G129" s="12" t="inlineStr">
+        <is>
+          <t>3+ RR groups, one custom-renamed</t>
+        </is>
+      </c>
+      <c r="H129" s="12" t="inlineStr">
+        <is>
+          <t>1. Rename Group B. 2. Dissolve Group A. 3. Observe letters.</t>
+        </is>
+      </c>
+      <c r="I129" s="12" t="inlineStr">
+        <is>
+          <t>Letters re-derive positionally at render (rrGroupLabels); the custom label survives verbatim; no duplicate or skipped letters.</t>
+        </is>
+      </c>
+      <c r="J129" s="12" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="K129" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="12" t="inlineStr">
+        <is>
+          <t>RR-06</t>
+        </is>
+      </c>
+      <c r="B130" s="12" t="inlineStr">
+        <is>
+          <t>Round Robin</t>
+        </is>
+      </c>
+      <c r="C130" s="12" t="inlineStr">
+        <is>
+          <t>Cross-group move reconciles both groups atomically</t>
+        </is>
+      </c>
+      <c r="D130" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E130" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F130" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G130" s="12" t="inlineStr">
+        <is>
+          <t>Two RR groups in the SAME draw, no played matches</t>
+        </is>
+      </c>
+      <c r="H130" s="12" t="inlineStr">
+        <is>
+          <t>1. Edit target group including the moved player; omit them from the source. 2. Save (handleSaveGroupEdit). 3. Kill the network mid-save and retry (failure sim).</t>
+        </is>
+      </c>
+      <c r="I130" s="12" t="inlineStr">
+        <is>
+          <t>Both groups' Firestore docs reconcile in one operation - the player never exists in both or neither after a completed save.</t>
+        </is>
+      </c>
+      <c r="J130" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K130" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="12" t="inlineStr">
+        <is>
+          <t>RR-07</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t>Round Robin</t>
+        </is>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>Moves touching a played group are refused</t>
+        </is>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F131" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G131" s="12" t="inlineStr">
+        <is>
+          <t>An RR group with one completed match</t>
+        </is>
+      </c>
+      <c r="H131" s="12" t="inlineStr">
+        <is>
+          <t>1. Try to move a player into it. 2. Try to move a player out of it.</t>
+        </is>
+      </c>
+      <c r="I131" s="12" t="inlineStr">
+        <is>
+          <t>Both refused with a clear message. The played group's docs are unchanged.</t>
+        </is>
+      </c>
+      <c r="J131" s="12" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="K131" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="12" t="inlineStr">
+        <is>
+          <t>RR-08</t>
+        </is>
+      </c>
+      <c r="B132" s="12" t="inlineStr">
+        <is>
+          <t>Round Robin</t>
+        </is>
+      </c>
+      <c r="C132" s="12" t="inlineStr">
+        <is>
+          <t>Empty group dissolves; lone player keeps a placeholder</t>
+        </is>
+      </c>
+      <c r="D132" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E132" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F132" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G132" s="12" t="inlineStr">
+        <is>
+          <t>A 2-player group</t>
+        </is>
+      </c>
+      <c r="H132" s="12" t="inlineStr">
+        <is>
+          <t>1. Move one player out. 2. Move the last player out.</t>
+        </is>
+      </c>
+      <c r="I132" s="12" t="inlineStr">
+        <is>
+          <t>With 1 player left: group keeps a placeholder match, lone player stays visible/movable. With 0: group dissolves.</t>
+        </is>
+      </c>
+      <c r="J132" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K132" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="12" t="inlineStr">
+        <is>
+          <t>RR-09</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="inlineStr">
+        <is>
+          <t>Round Robin</t>
+        </is>
+      </c>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>Add Group from unplaced players</t>
+        </is>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F133" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G133" s="12" t="inlineStr">
+        <is>
+          <t>Registered players not seated in any group</t>
+        </is>
+      </c>
+      <c r="H133" s="12" t="inlineStr">
+        <is>
+          <t>1. Use Add Group (handleCreateRRGroup).</t>
+        </is>
+      </c>
+      <c r="I133" s="12" t="inlineStr">
+        <is>
+          <t>New group created from the selected unplaced players; they disappear from the unplaced list.</t>
+        </is>
+      </c>
+      <c r="J133" s="12" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="K133" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="12" t="inlineStr">
+        <is>
+          <t>RR-10</t>
+        </is>
+      </c>
+      <c r="B134" s="12" t="inlineStr">
+        <is>
+          <t>Round Robin</t>
+        </is>
+      </c>
+      <c r="C134" s="12" t="inlineStr">
+        <is>
+          <t>Knockout generation seeds winners, leaves the rest manual</t>
+        </is>
+      </c>
+      <c r="D134" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E134" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F134" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G134" s="12" t="inlineStr">
+        <is>
+          <t>Completed RR group stage</t>
+        </is>
+      </c>
+      <c r="H134" s="12" t="inlineStr">
+        <is>
+          <t>1. Generate knockout at R8. 2. Inspect slots.</t>
+        </is>
+      </c>
+      <c r="I134" s="12" t="inlineStr">
+        <is>
+          <t>Every group winner auto-seeded (selectGroupWinners orders points → gamesWon; top seed in slot 1). Remaining slots are PLAYER_LOADING for manual fill. First-round byes do NOT auto-advance (manualFill). No automatic runner-up fill.</t>
+        </is>
+      </c>
+      <c r="J134" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K134" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="12" t="inlineStr">
+        <is>
+          <t>RR-11</t>
+        </is>
+      </c>
+      <c r="B135" s="12" t="inlineStr">
+        <is>
+          <t>Round Robin</t>
+        </is>
+      </c>
+      <c r="C135" s="12" t="inlineStr">
+        <is>
+          <t>Knockout rebuild allowed until played, then refused</t>
+        </is>
+      </c>
+      <c r="D135" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E135" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F135" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G135" s="12" t="inlineStr">
+        <is>
+          <t>Generated RR knockout</t>
+        </is>
+      </c>
+      <c r="H135" s="12" t="inlineStr">
+        <is>
+          <t>1. Re-select a size before any knockout match is scored. 2. Score one knockout match. 3. Re-select a size again.</t>
+        </is>
+      </c>
+      <c r="I135" s="12" t="inlineStr">
+        <is>
+          <t>Step 1 rebuilds. Step 3 is refused.</t>
+        </is>
+      </c>
+      <c r="J135" s="12" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="K135" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="12" t="inlineStr">
+        <is>
+          <t>RR-12</t>
+        </is>
+      </c>
+      <c r="B136" s="12" t="inlineStr">
+        <is>
+          <t>Round Robin</t>
+        </is>
+      </c>
+      <c r="C136" s="12" t="inlineStr">
+        <is>
+          <t>Sibling-draw self-heal removes double-seated player</t>
+        </is>
+      </c>
+      <c r="D136" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E136" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F136" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G136" s="12" t="inlineStr">
+        <is>
+          <t>Player seated in this draw's group AND in the sibling skill draw's groups (moved via participants/skill edit elsewhere)</t>
+        </is>
+      </c>
+      <c r="H136" s="12" t="inlineStr">
+        <is>
+          <t>1. Load the tournament page.</t>
+        </is>
+      </c>
+      <c r="I136" s="12" t="inlineStr">
+        <is>
+          <t>The background effect removes them from THIS draw's groups automatically - no dedicated move call, no duplicate seat left behind.</t>
+        </is>
+      </c>
+      <c r="J136" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K136" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="12" t="inlineStr">
+        <is>
+          <t>LJ-01</t>
+        </is>
+      </c>
+      <c r="B137" s="12" t="inlineStr">
+        <is>
+          <t>RR Late Joiners</t>
+        </is>
+      </c>
+      <c r="C137" s="12" t="inlineStr">
+        <is>
+          <t>Registration stays open after generation</t>
+        </is>
+      </c>
+      <c r="D137" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="F137" s="12" t="inlineStr">
+        <is>
+          <t>/events</t>
+        </is>
+      </c>
+      <c r="G137" s="12" t="inlineStr">
+        <is>
+          <t>RR event with a generated draw</t>
+        </is>
+      </c>
+      <c r="H137" s="12" t="inlineStr">
+        <is>
+          <t>1. Join the event.</t>
+        </is>
+      </c>
+      <c r="I137" s="12" t="inlineStr">
+        <is>
+          <t>Join succeeds (slotStatus bypassed for RR). The joiner is NOT sent to any reserves flow - they wait unplaced until the EOD script runs.</t>
+        </is>
+      </c>
+      <c r="J137" s="12" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="K137" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="12" t="inlineStr">
+        <is>
+          <t>LJ-02</t>
+        </is>
+      </c>
+      <c r="B138" s="12" t="inlineStr">
+        <is>
+          <t>RR Late Joiners</t>
+        </is>
+      </c>
+      <c r="C138" s="12" t="inlineStr">
+        <is>
+          <t>regroup-rr respects locked groups</t>
+        </is>
+      </c>
+      <c r="D138" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E138" s="12" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="F138" s="12" t="inlineStr">
+        <is>
+          <t>scripts</t>
+        </is>
+      </c>
+      <c r="G138" s="12" t="inlineStr">
+        <is>
+          <t>Groups of 4-5 players, a played 3-group, and an open 3-group matching the joiner's band</t>
+        </is>
+      </c>
+      <c r="H138" s="12" t="inlineStr">
+        <is>
+          <t>1. Run node scripts/regroup-rr.js --key ... (after --dry-run).</t>
+        </is>
+      </c>
+      <c r="I138" s="12" t="inlineStr">
+        <is>
+          <t>4-5-player groups and ANY played group are never touched. The joiner lands in the ≤3 group with a matching band (zone preferred).</t>
+        </is>
+      </c>
+      <c r="J138" s="12" t="inlineStr">
+        <is>
+          <t>Script</t>
+        </is>
+      </c>
+      <c r="K138" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="12" t="inlineStr">
+        <is>
+          <t>LJ-03</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="inlineStr">
+        <is>
+          <t>RR Late Joiners</t>
+        </is>
+      </c>
+      <c r="C139" s="12" t="inlineStr">
+        <is>
+          <t>Overflow forms new (band, zone) groups</t>
+        </is>
+      </c>
+      <c r="D139" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E139" s="12" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="F139" s="12" t="inlineStr">
+        <is>
+          <t>scripts</t>
+        </is>
+      </c>
+      <c r="G139" s="12" t="inlineStr">
+        <is>
+          <t>More joiners than open-group capacity</t>
+        </is>
+      </c>
+      <c r="H139" s="12" t="inlineStr">
+        <is>
+          <t>1. Run the script.</t>
+        </is>
+      </c>
+      <c r="I139" s="12" t="inlineStr">
+        <is>
+          <t>Overflow players form new groups per (band, zone) via splitEvenly - never crammed into locked groups.</t>
+        </is>
+      </c>
+      <c r="J139" s="12" t="inlineStr">
+        <is>
+          <t>Script</t>
+        </is>
+      </c>
+      <c r="K139" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="12" t="inlineStr">
+        <is>
+          <t>LJ-04</t>
+        </is>
+      </c>
+      <c r="B140" s="12" t="inlineStr">
+        <is>
+          <t>RR Late Joiners</t>
+        </is>
+      </c>
+      <c r="C140" s="12" t="inlineStr">
+        <is>
+          <t>Dry-run writes nothing; second run is a no-op</t>
+        </is>
+      </c>
+      <c r="D140" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E140" s="12" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="F140" s="12" t="inlineStr">
+        <is>
+          <t>scripts</t>
+        </is>
+      </c>
+      <c r="G140" s="12" t="inlineStr">
+        <is>
+          <t>Pending late joiners</t>
+        </is>
+      </c>
+      <c r="H140" s="12" t="inlineStr">
+        <is>
+          <t>1. Run with --dry-run; diff Firestore. 2. Run live. 3. Run live again.</t>
+        </is>
+      </c>
+      <c r="I140" s="12" t="inlineStr">
+        <is>
+          <t>Dry-run: zero writes. Second live run with no new joiners: zero writes (idempotent).</t>
+        </is>
+      </c>
+      <c r="J140" s="12" t="inlineStr">
+        <is>
+          <t>Script</t>
+        </is>
+      </c>
+      <c r="K140" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="12" t="inlineStr">
+        <is>
+          <t>PT-01</t>
+        </is>
+      </c>
+      <c r="B141" s="12" t="inlineStr">
+        <is>
+          <t>Points &amp; Stats</t>
+        </is>
+      </c>
+      <c r="C141" s="12" t="inlineStr">
+        <is>
+          <t>RR group win scores 3/1 - including walkovers</t>
+        </is>
+      </c>
+      <c r="D141" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E141" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F141" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G141" s="12" t="inlineStr">
+        <is>
+          <t>RR group match, one normal and one walkover</t>
+        </is>
+      </c>
+      <c r="H141" s="12" t="inlineStr">
+        <is>
+          <t>1. Score a normal win. 2. Score a walkover win.</t>
+        </is>
+      </c>
+      <c r="I141" s="12" t="inlineStr">
+        <is>
+          <t>Both: winner +3, loser +1, applied live per match. The old isWalkover?1:3 penalty must NOT reappear. computeGroupStandings shows the same 3/1.</t>
+        </is>
+      </c>
+      <c r="J141" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K141" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="12" t="inlineStr">
+        <is>
+          <t>PT-02</t>
+        </is>
+      </c>
+      <c r="B142" s="12" t="inlineStr">
+        <is>
+          <t>Points &amp; Stats</t>
+        </is>
+      </c>
+      <c r="C142" s="12" t="inlineStr">
+        <is>
+          <t>Knockout round points table</t>
+        </is>
+      </c>
+      <c r="D142" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E142" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F142" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G142" s="12" t="inlineStr">
+        <is>
+          <t>Bracket matches at each round</t>
+        </is>
+      </c>
+      <c r="H142" s="12" t="inlineStr">
+        <is>
+          <t>1. Score losses at R32/R16/QF/SF/F and a final win.</t>
+        </is>
+      </c>
+      <c r="I142" s="12" t="inlineStr">
+        <is>
+          <t>Loser: R32=1, R16=2, QF=3, SF=5, F=10. Winner: +20 on the FINAL only (winnerPointsApply). Non-final winners score nothing at that moment.</t>
+        </is>
+      </c>
+      <c r="J142" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K142" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="12" t="inlineStr">
+        <is>
+          <t>PT-03</t>
+        </is>
+      </c>
+      <c r="B143" s="12" t="inlineStr">
+        <is>
+          <t>Points &amp; Stats</t>
+        </is>
+      </c>
+      <c r="C143" s="12" t="inlineStr">
+        <is>
+          <t>RR +5 completion bonus paid once and stamped</t>
+        </is>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E143" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F143" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G143" s="12" t="inlineStr">
+        <is>
+          <t>An RR group one match away from complete</t>
+        </is>
+      </c>
+      <c r="H143" s="12" t="inlineStr">
+        <is>
+          <t>1. Score the last match. 2. Inspect all group match docs + both players' stats.</t>
+        </is>
+      </c>
+      <c r="I143" s="12" t="inlineStr">
+        <is>
+          <t>+5 paid to each group member in a separate commit; every match in the group stamped rr_group_bonus_v2: true.</t>
+        </is>
+      </c>
+      <c r="J143" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K143" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="12" t="inlineStr">
+        <is>
+          <t>PT-04</t>
+        </is>
+      </c>
+      <c r="B144" s="12" t="inlineStr">
+        <is>
+          <t>Points &amp; Stats</t>
+        </is>
+      </c>
+      <c r="C144" s="12" t="inlineStr">
+        <is>
+          <t>Corrected match does not double-pay the bonus</t>
+        </is>
+      </c>
+      <c r="D144" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E144" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F144" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G144" s="12" t="inlineStr">
+        <is>
+          <t>A completed, bonus-stamped group; one match score corrected</t>
+        </is>
+      </c>
+      <c r="H144" s="12" t="inlineStr">
+        <is>
+          <t>1. Edit and re-confirm the corrected match.</t>
+        </is>
+      </c>
+      <c r="I144" s="12" t="inlineStr">
+        <is>
+          <t>No second +5 (the stamp is checked before paying). status !== 'complete' alone is NOT the guard.</t>
+        </is>
+      </c>
+      <c r="J144" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K144" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="12" t="inlineStr">
+        <is>
+          <t>PT-05</t>
+        </is>
+      </c>
+      <c r="B145" s="12" t="inlineStr">
+        <is>
+          <t>Points &amp; Stats</t>
+        </is>
+      </c>
+      <c r="C145" s="12" t="inlineStr">
+        <is>
+          <t>Reset reverses the bonus only if stamped</t>
+        </is>
+      </c>
+      <c r="D145" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E145" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F145" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G145" s="12" t="inlineStr">
+        <is>
+          <t>One group with the stamp, one where the bonus commit failed (simulate)</t>
+        </is>
+      </c>
+      <c r="H145" s="12" t="inlineStr">
+        <is>
+          <t>1. Reset both draws. 2. Compare stats deltas.</t>
+        </is>
+      </c>
+      <c r="I145" s="12" t="inlineStr">
+        <is>
+          <t>Stamped group: -5 reversed. Unstamped: NOT deducted - reverseRRBonusesInto checks the stamp, so players never lose points they were never paid.</t>
+        </is>
+      </c>
+      <c r="J145" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K145" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="12" t="inlineStr">
+        <is>
+          <t>PT-06</t>
+        </is>
+      </c>
+      <c r="B146" s="12" t="inlineStr">
+        <is>
+          <t>Points &amp; Stats</t>
+        </is>
+      </c>
+      <c r="C146" s="12" t="inlineStr">
+        <is>
+          <t>Doubles partner credits apply and reverse together</t>
+        </is>
+      </c>
+      <c r="D146" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E146" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F146" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G146" s="12" t="inlineStr">
+        <is>
+          <t>A doubles match with partner_uid on both captains</t>
+        </is>
+      </c>
+      <c r="H146" s="12" t="inlineStr">
+        <is>
+          <t>1. Score the match; check all four players' stats. 2. Reset the draw; re-check.</t>
+        </is>
+      </c>
+      <c r="I146" s="12" t="inlineStr">
+        <is>
+          <t>Partner credits land in the same scoring batch, and the reset reverses them via the same per-captain partner_uid map (doubles_partner_pts_v2 backfill stamp respected).</t>
+        </is>
+      </c>
+      <c r="J146" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K146" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="12" t="inlineStr">
+        <is>
+          <t>PT-07</t>
+        </is>
+      </c>
+      <c r="B147" s="12" t="inlineStr">
+        <is>
+          <t>Points &amp; Stats</t>
+        </is>
+      </c>
+      <c r="C147" s="12" t="inlineStr">
+        <is>
+          <t>Blank winner_uid is rejected</t>
+        </is>
+      </c>
+      <c r="D147" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E147" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F147" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G147" s="12" t="inlineStr">
+        <is>
+          <t>Score modal open on any match</t>
+        </is>
+      </c>
+      <c r="H147" s="12" t="inlineStr">
+        <is>
+          <t>1. Submit a score with no winner selected (force via devtools if UI blocks it).</t>
+        </is>
+      </c>
+      <c r="I147" s="12" t="inlineStr">
+        <is>
+          <t>Rejected outright. The match must NOT complete showing player 2 as winner, credit player 1 a loss, or write an empty uid into the next round.</t>
+        </is>
+      </c>
+      <c r="J147" s="12" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="K147" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="12" t="inlineStr">
+        <is>
+          <t>PT-08</t>
+        </is>
+      </c>
+      <c r="B148" s="12" t="inlineStr">
+        <is>
+          <t>Points &amp; Stats</t>
+        </is>
+      </c>
+      <c r="C148" s="12" t="inlineStr">
+        <is>
+          <t>completed_at pinned to first scoring</t>
+        </is>
+      </c>
+      <c r="D148" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E148" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F148" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G148" s="12" t="inlineStr">
+        <is>
+          <t>A completed match</t>
+        </is>
+      </c>
+      <c r="H148" s="12" t="inlineStr">
+        <is>
+          <t>1. Edit the score days later. 2. Inspect timestamps and anything sorted by completed_at (streaks, months active).</t>
+        </is>
+      </c>
+      <c r="I148" s="12" t="inlineStr">
+        <is>
+          <t>completed_at unchanged; the edit stamps score_edited_at instead. Sorted stats stay correct.</t>
+        </is>
+      </c>
+      <c r="J148" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K148" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="12" t="inlineStr">
+        <is>
+          <t>PT-09</t>
+        </is>
+      </c>
+      <c r="B149" s="12" t="inlineStr">
+        <is>
+          <t>Points &amp; Stats</t>
+        </is>
+      </c>
+      <c r="C149" s="12" t="inlineStr">
+        <is>
+          <t>Client/server points parity</t>
+        </is>
+      </c>
+      <c r="D149" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E149" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F149" s="12" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="G149" s="12" t="inlineStr">
+        <is>
+          <t>Same tasks/{uid} doc fed to both</t>
+        </is>
+      </c>
+      <c r="H149" s="12" t="inlineStr">
+        <is>
+          <t>1. Compute taskPoints() (useTasks.ts) and earnedRsPoints (functions/lib/points.js) for identical fixture docs incl. SETUP_POINTS and every tier boundary.</t>
+        </is>
+      </c>
+      <c r="I149" s="12" t="inlineStr">
+        <is>
+          <t>Identical totals for every fixture. This guards the hand-synced twin pair - run it whenever taskCatalog.ts or lib/points.js changes.</t>
+        </is>
+      </c>
+      <c r="J149" s="12" t="inlineStr">
+        <is>
+          <t>Automated unit</t>
+        </is>
+      </c>
+      <c r="K149" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="12" t="inlineStr">
+        <is>
+          <t>LD-01</t>
+        </is>
+      </c>
+      <c r="B150" s="12" t="inlineStr">
+        <is>
+          <t>Ladder &amp; Friendlies</t>
+        </is>
+      </c>
+      <c r="C150" s="12" t="inlineStr">
+        <is>
+          <t>Double-tap confirm applies points once</t>
+        </is>
+      </c>
+      <c r="D150" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E150" s="12" t="inlineStr">
+        <is>
+          <t>Organizer</t>
+        </is>
+      </c>
+      <c r="F150" s="12" t="inlineStr">
+        <is>
+          <t>/matches</t>
+        </is>
+      </c>
+      <c r="G150" s="12" t="inlineStr">
+        <is>
+          <t>A reported challenge; two confirms fired near-simultaneously (mobile double-tap sim)</t>
+        </is>
+      </c>
+      <c r="H150" s="12" t="inlineStr">
+        <is>
+          <t>1. Fire confirmChallenge twice concurrently.</t>
+        </is>
+      </c>
+      <c r="I150" s="12" t="inlineStr">
+        <is>
+          <t>Exactly one +/-3 application (runTransaction reads the applied flag inside the txn). Never winner +6 / loser -6.</t>
+        </is>
+      </c>
+      <c r="J150" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K150" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="12" t="inlineStr">
+        <is>
+          <t>LD-02</t>
+        </is>
+      </c>
+      <c r="B151" s="12" t="inlineStr">
+        <is>
+          <t>Ladder &amp; Friendlies</t>
+        </is>
+      </c>
+      <c r="C151" s="12" t="inlineStr">
+        <is>
+          <t>Loser deduction floors at 0</t>
+        </is>
+      </c>
+      <c r="D151" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E151" s="12" t="inlineStr">
+        <is>
+          <t>Organizer</t>
+        </is>
+      </c>
+      <c r="F151" s="12" t="inlineStr">
+        <is>
+          <t>/matches</t>
+        </is>
+      </c>
+      <c r="G151" s="12" t="inlineStr">
+        <is>
+          <t>Loser has leaguePoints26 = 1</t>
+        </is>
+      </c>
+      <c r="H151" s="12" t="inlineStr">
+        <is>
+          <t>1. Confirm the challenge.</t>
+        </is>
+      </c>
+      <c r="I151" s="12" t="inlineStr">
+        <is>
+          <t>Loser lands at 0, not -2 (read-then-write floor inside the transaction).</t>
+        </is>
+      </c>
+      <c r="J151" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K151" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="12" t="inlineStr">
+        <is>
+          <t>LD-03</t>
+        </is>
+      </c>
+      <c r="B152" s="12" t="inlineStr">
+        <is>
+          <t>Ladder &amp; Friendlies</t>
+        </is>
+      </c>
+      <c r="C152" s="12" t="inlineStr">
+        <is>
+          <t>Player with no stats doc doesn't strand the challenge</t>
+        </is>
+      </c>
+      <c r="D152" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E152" s="12" t="inlineStr">
+        <is>
+          <t>Organizer</t>
+        </is>
+      </c>
+      <c r="F152" s="12" t="inlineStr">
+        <is>
+          <t>/matches</t>
+        </is>
+      </c>
+      <c r="G152" s="12" t="inlineStr">
+        <is>
+          <t>One participant has no stats/{uid} doc</t>
+        </is>
+      </c>
+      <c r="H152" s="12" t="inlineStr">
+        <is>
+          <t>1. Confirm the challenge.</t>
+        </is>
+      </c>
+      <c r="I152" s="12" t="inlineStr">
+        <is>
+          <t>All three writes use set(merge) - the confirm succeeds, no challenge stuck in 'reported'.</t>
+        </is>
+      </c>
+      <c r="J152" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K152" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="12" t="inlineStr">
+        <is>
+          <t>LD-04</t>
+        </is>
+      </c>
+      <c r="B153" s="12" t="inlineStr">
+        <is>
+          <t>Ladder &amp; Friendlies</t>
+        </is>
+      </c>
+      <c r="C153" s="12" t="inlineStr">
+        <is>
+          <t>Connections only on acceptance</t>
+        </is>
+      </c>
+      <c r="D153" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E153" s="12" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="F153" s="12" t="inlineStr">
+        <is>
+          <t>/matches</t>
+        </is>
+      </c>
+      <c r="G153" s="12" t="inlineStr">
+        <is>
+          <t>Player A sends a challenge to B; B never responds. Separately, C accepts one from A</t>
+        </is>
+      </c>
+      <c r="H153" s="12" t="inlineStr">
+        <is>
+          <t>1. Check connections and contact readability for both pairs.</t>
+        </is>
+      </c>
+      <c r="I153" s="12" t="inlineStr">
+        <is>
+          <t>A__B (open): NO connection, B's contacts unreadable to A - spamming challenges harvests nothing. A__C (accepted): connection exists, contacts readable both ways.</t>
+        </is>
+      </c>
+      <c r="J153" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K153" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="12" t="inlineStr">
+        <is>
+          <t>LD-05</t>
+        </is>
+      </c>
+      <c r="B154" s="12" t="inlineStr">
+        <is>
+          <t>Ladder &amp; Friendlies</t>
+        </is>
+      </c>
+      <c r="C154" s="12" t="inlineStr">
+        <is>
+          <t>Suggestion filters allocate by constraint, never overlap</t>
+        </is>
+      </c>
+      <c r="D154" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E154" s="12" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="F154" s="12" t="inlineStr">
+        <is>
+          <t>/matches</t>
+        </is>
+      </c>
+      <c r="G154" s="12" t="inlineStr">
+        <is>
+          <t>Enough candidates for all three filters</t>
+        </is>
+      </c>
+      <c r="H154" s="12" t="inlineStr">
+        <is>
+          <t>1. Open the page repeatedly across a weekly refresh. 2. Compare the three lists and roll the dice.</t>
+        </is>
+      </c>
+      <c r="I154" s="12" t="inlineStr">
+        <is>
+          <t>Nearby (smallest pool) allocates first; the three visible sets never overlap; dice draws come from each filter's spare block, still non-overlapping.</t>
+        </is>
+      </c>
+      <c r="J154" s="12" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="K154" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="12" t="inlineStr">
+        <is>
+          <t>RW-01</t>
+        </is>
+      </c>
+      <c r="B155" s="12" t="inlineStr">
+        <is>
+          <t>Rewards &amp; Services</t>
+        </is>
+      </c>
+      <c r="C155" s="12" t="inlineStr">
+        <is>
+          <t>Redeemable balance is server-computed</t>
+        </is>
+      </c>
+      <c r="D155" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E155" s="12" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="F155" s="12" t="inlineStr">
+        <is>
+          <t>/marketplace</t>
+        </is>
+      </c>
+      <c r="G155" s="12" t="inlineStr">
+        <is>
+          <t>Player with known earned RS points; client state tampered via devtools</t>
+        </is>
+      </c>
+      <c r="H155" s="12" t="inlineStr">
+        <is>
+          <t>1. Inflate the client-side balance. 2. Attempt redeemReward above the real balance.</t>
+        </is>
+      </c>
+      <c r="I155" s="12" t="inlineStr">
+        <is>
+          <t>Callable recomputes earnedRsPoints (lib/points.js) server-side and rejects. Client numbers are display-only.</t>
+        </is>
+      </c>
+      <c r="J155" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K155" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="12" t="inlineStr">
+        <is>
+          <t>RW-02</t>
+        </is>
+      </c>
+      <c r="B156" s="12" t="inlineStr">
+        <is>
+          <t>Rewards &amp; Services</t>
+        </is>
+      </c>
+      <c r="C156" s="12" t="inlineStr">
+        <is>
+          <t>Redemption doc id is the coupon code; reward ids stay bare</t>
+        </is>
+      </c>
+      <c r="D156" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E156" s="12" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="F156" s="12" t="inlineStr">
+        <is>
+          <t>/marketplace</t>
+        </is>
+      </c>
+      <c r="G156" s="12" t="inlineStr">
+        <is>
+          <t>An offer row in tasks (bare doc id)</t>
+        </is>
+      </c>
+      <c r="H156" s="12" t="inlineStr">
+        <is>
+          <t>1. Redeem an offer. 2. Inspect the redemptions doc.</t>
+        </is>
+      </c>
+      <c r="I156" s="12" t="inlineStr">
+        <is>
+          <t>Doc id = coupon code; reward_id resolves tasks/{rewardId} directly (no prefix). A prefixed id would break rewards.js resolution.</t>
+        </is>
+      </c>
+      <c r="J156" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K156" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="12" t="inlineStr">
+        <is>
+          <t>RW-03</t>
+        </is>
+      </c>
+      <c r="B157" s="12" t="inlineStr">
+        <is>
+          <t>Rewards &amp; Services</t>
+        </is>
+      </c>
+      <c r="C157" s="12" t="inlineStr">
+        <is>
+          <t>Coupon lifecycle callables</t>
+        </is>
+      </c>
+      <c r="D157" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E157" s="12" t="inlineStr">
+        <is>
+          <t>Provider+Player</t>
+        </is>
+      </c>
+      <c r="F157" s="12" t="inlineStr">
+        <is>
+          <t>/marketplace</t>
+        </is>
+      </c>
+      <c r="G157" s="12" t="inlineStr">
+        <is>
+          <t>An issued redemption</t>
+        </is>
+      </c>
+      <c r="H157" s="12" t="inlineStr">
+        <is>
+          <t>1. Provider markCouponUsed. 2. flagCoupon. 3. Player requestCancellation. 4. Organizer reviewRedemption.</t>
+        </is>
+      </c>
+      <c r="I157" s="12" t="inlineStr">
+        <is>
+          <t>Each transition works only for the authorized role and is rejected for others; state is consistent after each step.</t>
+        </is>
+      </c>
+      <c r="J157" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K157" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="12" t="inlineStr">
+        <is>
+          <t>RW-04</t>
+        </is>
+      </c>
+      <c r="B158" s="12" t="inlineStr">
+        <is>
+          <t>Rewards &amp; Services</t>
+        </is>
+      </c>
+      <c r="C158" s="12" t="inlineStr">
+        <is>
+          <t>Provider reads only their own redemptions</t>
+        </is>
+      </c>
+      <c r="D158" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E158" s="12" t="inlineStr">
+        <is>
+          <t>Provider</t>
+        </is>
+      </c>
+      <c r="F158" s="12" t="inlineStr">
+        <is>
+          <t>/marketplace</t>
+        </is>
+      </c>
+      <c r="G158" s="12" t="inlineStr">
+        <is>
+          <t>preferences.stringer_id / coach_id set (set-stringer.mjs)</t>
+        </is>
+      </c>
+      <c r="H158" s="12" t="inlineStr">
+        <is>
+          <t>1. Read own redemptions. 2. Attempt to read another provider's.</t>
+        </is>
+      </c>
+      <c r="I158" s="12" t="inlineStr">
+        <is>
+          <t>Own: allowed via isProviderFor. Other's: denied by rules.</t>
+        </is>
+      </c>
+      <c r="J158" s="12" t="inlineStr">
+        <is>
+          <t>Rules unit</t>
+        </is>
+      </c>
+      <c r="K158" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="12" t="inlineStr">
+        <is>
+          <t>RW-05</t>
+        </is>
+      </c>
+      <c r="B159" s="12" t="inlineStr">
+        <is>
+          <t>Rewards &amp; Services</t>
+        </is>
+      </c>
+      <c r="C159" s="12" t="inlineStr">
+        <is>
+          <t>Group lesson capacity</t>
+        </is>
+      </c>
+      <c r="D159" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E159" s="12" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="F159" s="12" t="inlineStr">
+        <is>
+          <t>/marketplace</t>
+        </is>
+      </c>
+      <c r="G159" s="12" t="inlineStr">
+        <is>
+          <t>A group_lessons month near capacity</t>
+        </is>
+      </c>
+      <c r="H159" s="12" t="inlineStr">
+        <is>
+          <t>1. joinGroupLesson to fill the roster. 2. One more join. 3. leaveGroupLesson.</t>
+        </is>
+      </c>
+      <c r="I159" s="12" t="inlineStr">
+        <is>
+          <t>Join beyond capacity rejected server-side; leave frees the seat; roster doc consistent throughout.</t>
+        </is>
+      </c>
+      <c r="J159" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K159" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="12" t="inlineStr">
+        <is>
+          <t>RW-06</t>
+        </is>
+      </c>
+      <c r="B160" s="12" t="inlineStr">
+        <is>
+          <t>Rewards &amp; Services</t>
+        </is>
+      </c>
+      <c r="C160" s="12" t="inlineStr">
+        <is>
+          <t>Logged-out browsing, zero balance</t>
+        </is>
+      </c>
+      <c r="D160" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E160" s="12" t="inlineStr">
+        <is>
+          <t>Visitor</t>
+        </is>
+      </c>
+      <c r="F160" s="12" t="inlineStr">
+        <is>
+          <t>/marketplace</t>
+        </is>
+      </c>
+      <c r="G160" s="12" t="inlineStr">
+        <is>
+          <t>Signed out</t>
+        </is>
+      </c>
+      <c r="H160" s="12" t="inlineStr">
+        <is>
+          <t>1. Browse Services offers. 2. Attempt any redemption path.</t>
+        </is>
+      </c>
+      <c r="I160" s="12" t="inlineStr">
+        <is>
+          <t>Offers fully browsable (deliberate); balance reads 0; nothing redeemable; providers' contact details withheld.</t>
+        </is>
+      </c>
+      <c r="J160" s="12" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="K160" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="12" t="inlineStr">
+        <is>
+          <t>RW-07</t>
+        </is>
+      </c>
+      <c r="B161" s="12" t="inlineStr">
+        <is>
+          <t>Rewards &amp; Services</t>
+        </is>
+      </c>
+      <c r="C161" s="12" t="inlineStr">
+        <is>
+          <t>Server-only collections reject client writes</t>
+        </is>
+      </c>
+      <c r="D161" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E161" s="12" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="F161" s="12" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="G161" s="12" t="inlineStr">
+        <is>
+          <t>Signed-in user with devtools</t>
+        </is>
+      </c>
+      <c r="H161" s="12" t="inlineStr">
+        <is>
+          <t>1. Attempt direct Firestore writes to offers, redemptions, group_lessons, connections, public_contacts, notifications, site_stats, ranking_history.</t>
+        </is>
+      </c>
+      <c r="I161" s="12" t="inlineStr">
+        <is>
+          <t>Every write denied. These are Cloud-Function-only surfaces.</t>
+        </is>
+      </c>
+      <c r="J161" s="12" t="inlineStr">
+        <is>
+          <t>Rules unit</t>
+        </is>
+      </c>
+      <c r="K161" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="12" t="inlineStr">
+        <is>
+          <t>MP-01</t>
+        </is>
+      </c>
+      <c r="B162" s="12" t="inlineStr">
+        <is>
+          <t>Marketplace &amp; Contacts</t>
+        </is>
+      </c>
+      <c r="C162" s="12" t="inlineStr">
+        <is>
+          <t>First listing publishes contactability</t>
+        </is>
+      </c>
+      <c r="D162" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E162" s="12" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="F162" s="12" t="inlineStr">
+        <is>
+          <t>/marketplace</t>
+        </is>
+      </c>
+      <c r="G162" s="12" t="inlineStr">
+        <is>
+          <t>Player with no listings; a stranger signed in</t>
+        </is>
+      </c>
+      <c r="H162" s="12" t="inlineStr">
+        <is>
+          <t>1. Post a listing. 2. Stranger opens it and reads the poster's contacts.</t>
+        </is>
+      </c>
+      <c r="I162" s="12" t="inlineStr">
+        <is>
+          <t>onListingContact writes public_contacts/{uid}; the stranger's contact read now succeeds. That is the deliberate carve-out - posting IS the invitation.</t>
+        </is>
+      </c>
+      <c r="J162" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K162" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="12" t="inlineStr">
+        <is>
+          <t>MP-02</t>
+        </is>
+      </c>
+      <c r="B163" s="12" t="inlineStr">
+        <is>
+          <t>Marketplace &amp; Contacts</t>
+        </is>
+      </c>
+      <c r="C163" s="12" t="inlineStr">
+        <is>
+          <t>Deleting the last listing revokes it</t>
+        </is>
+      </c>
+      <c r="D163" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E163" s="12" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="F163" s="12" t="inlineStr">
+        <is>
+          <t>/marketplace</t>
+        </is>
+      </c>
+      <c r="G163" s="12" t="inlineStr">
+        <is>
+          <t>Poster from MP-01 with exactly one listing</t>
+        </is>
+      </c>
+      <c r="H163" s="12" t="inlineStr">
+        <is>
+          <t>1. Delete the listing. 2. Stranger retries the contact read.</t>
+        </is>
+      </c>
+      <c r="I163" s="12" t="inlineStr">
+        <is>
+          <t>Marker removed; read denied again. With two listings, deleting one keeps the marker.</t>
+        </is>
+      </c>
+      <c r="J163" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K163" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="12" t="inlineStr">
+        <is>
+          <t>MP-03</t>
+        </is>
+      </c>
+      <c r="B164" s="12" t="inlineStr">
+        <is>
+          <t>Marketplace &amp; Contacts</t>
+        </is>
+      </c>
+      <c r="C164" s="12" t="inlineStr">
+        <is>
+          <t>Listing create rules</t>
+        </is>
+      </c>
+      <c r="D164" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E164" s="12" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="F164" s="12" t="inlineStr">
+        <is>
+          <t>/marketplace</t>
+        </is>
+      </c>
+      <c r="G164" s="12" t="inlineStr">
+        <is>
+          <t>Signed in</t>
+        </is>
+      </c>
+      <c r="H164" s="12" t="inlineStr">
+        <is>
+          <t>1. Create with kind 'rent' and 'sell'. 2. Attempt kind 'trade', status 'sold', or another uid.</t>
+        </is>
+      </c>
+      <c r="I164" s="12" t="inlineStr">
+        <is>
+          <t>Valid kinds/status/uid pass; everything else denied by rules.</t>
+        </is>
+      </c>
+      <c r="J164" s="12" t="inlineStr">
+        <is>
+          <t>Rules unit</t>
+        </is>
+      </c>
+      <c r="K164" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="12" t="inlineStr">
+        <is>
+          <t>MP-04</t>
+        </is>
+      </c>
+      <c r="B165" s="12" t="inlineStr">
+        <is>
+          <t>Marketplace &amp; Contacts</t>
+        </is>
+      </c>
+      <c r="C165" s="12" t="inlineStr">
+        <is>
+          <t>Listing photos are moderated</t>
+        </is>
+      </c>
+      <c r="D165" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E165" s="12" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="F165" s="12" t="inlineStr">
+        <is>
+          <t>/marketplace</t>
+        </is>
+      </c>
+      <c r="G165" s="12" t="inlineStr">
+        <is>
+          <t>Signed in</t>
+        </is>
+      </c>
+      <c r="H165" s="12" t="inlineStr">
+        <is>
+          <t>1. Upload a listing photo &gt;5MB, a non-image, and a SafeSearch-unsafe image (staged).</t>
+        </is>
+      </c>
+      <c r="I165" s="12" t="inlineStr">
+        <is>
+          <t>Size/type rejected by storage.rules at listings/{uid}/. Unsafe image removed/flagged by moderateUploadedImage.</t>
+        </is>
+      </c>
+      <c r="J165" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K165" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="12" t="inlineStr">
+        <is>
+          <t>MP-05</t>
+        </is>
+      </c>
+      <c r="B166" s="12" t="inlineStr">
+        <is>
+          <t>Marketplace &amp; Contacts</t>
+        </is>
+      </c>
+      <c r="C166" s="12" t="inlineStr">
+        <is>
+          <t>One denied contact never blanks the page</t>
+        </is>
+      </c>
+      <c r="D166" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E166" s="12" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="F166" s="12" t="inlineStr">
+        <is>
+          <t>/matches</t>
+        </is>
+      </c>
+      <c r="G166" s="12" t="inlineStr">
+        <is>
+          <t>A page listing several opponents where one connection doc hasn't landed yet</t>
+        </is>
+      </c>
+      <c r="H166" s="12" t="inlineStr">
+        <is>
+          <t>1. Load contact details for all rows.</t>
+        </is>
+      </c>
+      <c r="I166" s="12" t="inlineStr">
+        <is>
+          <t>Each read has its own .catch(); the one denial renders as 'not available' while every other contact shows. No Promise.all() collapse.</t>
+        </is>
+      </c>
+      <c r="J166" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K166" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="12" t="inlineStr">
+        <is>
+          <t>MP-06</t>
+        </is>
+      </c>
+      <c r="B167" s="12" t="inlineStr">
+        <is>
+          <t>Marketplace &amp; Contacts</t>
+        </is>
+      </c>
+      <c r="C167" s="12" t="inlineStr">
+        <is>
+          <t>pairId parity between trigger and rules</t>
+        </is>
+      </c>
+      <c r="D167" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E167" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F167" s="12" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="G167" s="12" t="inlineStr">
+        <is>
+          <t>Fixture uid pairs in both orders</t>
+        </is>
+      </c>
+      <c r="H167" s="12" t="inlineStr">
+        <is>
+          <t>1. Compute pairId in functions/connections.js and evaluate the rules recompute for the same pairs (rules emulator).</t>
+        </is>
+      </c>
+      <c r="I167" s="12" t="inlineStr">
+        <is>
+          <t>Identical ids both ways for every pair. Divergence breaks every contact read in the app - run on any change to either file.</t>
+        </is>
+      </c>
+      <c r="J167" s="12" t="inlineStr">
+        <is>
+          <t>Automated unit</t>
+        </is>
+      </c>
+      <c r="K167" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="12" t="inlineStr">
+        <is>
+          <t>NT-01</t>
+        </is>
+      </c>
+      <c r="B168" s="12" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C168" s="12" t="inlineStr">
+        <is>
+          <t>Zone-change and schedule requests notify the right person</t>
+        </is>
+      </c>
+      <c r="D168" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E168" s="12" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="F168" s="12" t="inlineStr">
+        <is>
+          <t>/matches</t>
+        </is>
+      </c>
+      <c r="G168" s="12" t="inlineStr">
+        <is>
+          <t>A zone change request and a schedule proposal</t>
+        </is>
+      </c>
+      <c r="H168" s="12" t="inlineStr">
+        <is>
+          <t>1. Trigger each. 2. Check recipients' feeds.</t>
+        </is>
+      </c>
+      <c r="I168" s="12" t="inlineStr">
+        <is>
+          <t>onZoneChangeRequested notifies the creator; onScheduleRequested notifies the opponent. No self-notification.</t>
+        </is>
+      </c>
+      <c r="J168" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K168" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="12" t="inlineStr">
+        <is>
+          <t>NT-02</t>
+        </is>
+      </c>
+      <c r="B169" s="12" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C169" s="12" t="inlineStr">
+        <is>
+          <t>Recipient-only access</t>
+        </is>
+      </c>
+      <c r="D169" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E169" s="12" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="F169" s="12" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="G169" s="12" t="inlineStr">
+        <is>
+          <t>Notifications for two different users</t>
+        </is>
+      </c>
+      <c r="H169" s="12" t="inlineStr">
+        <is>
+          <t>1. Read/mark-read/delete own. 2. Attempt the same on another user's. 3. Attempt client create.</t>
+        </is>
+      </c>
+      <c r="I169" s="12" t="inlineStr">
+        <is>
+          <t>Own: allowed (update restricted to read/read_at). Other's: denied. Create: always denied.</t>
+        </is>
+      </c>
+      <c r="J169" s="12" t="inlineStr">
+        <is>
+          <t>Rules unit</t>
+        </is>
+      </c>
+      <c r="K169" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="12" t="inlineStr">
+        <is>
+          <t>NT-03</t>
+        </is>
+      </c>
+      <c r="B170" s="12" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C170" s="12" t="inlineStr">
+        <is>
+          <t>Score submission lifecycle notifies both ways</t>
+        </is>
+      </c>
+      <c r="D170" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E170" s="12" t="inlineStr">
+        <is>
+          <t>Player+Creator</t>
+        </is>
+      </c>
+      <c r="F170" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G170" s="12" t="inlineStr">
+        <is>
+          <t>A player-filed score submission</t>
+        </is>
+      </c>
+      <c r="H170" s="12" t="inlineStr">
+        <is>
+          <t>1. Player files (category score_submission). 2. Creator confirms (deletes it).</t>
+        </is>
+      </c>
+      <c r="I170" s="12" t="inlineStr">
+        <is>
+          <t>onScoreSubmitted notifies the creator; onScoreSubmissionResolved notifies the submitter on deletion.</t>
+        </is>
+      </c>
+      <c r="J170" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K170" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="12" t="inlineStr">
+        <is>
+          <t>NT-04</t>
+        </is>
+      </c>
+      <c r="B171" s="12" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C171" s="12" t="inlineStr">
+        <is>
+          <t>Prune removes old notifications</t>
+        </is>
+      </c>
+      <c r="D171" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E171" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F171" s="12" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="G171" s="12" t="inlineStr">
+        <is>
+          <t>Feed entries older than the prune window</t>
+        </is>
+      </c>
+      <c r="H171" s="12" t="inlineStr">
+        <is>
+          <t>1. Run/await pruneNotifications.</t>
+        </is>
+      </c>
+      <c r="I171" s="12" t="inlineStr">
+        <is>
+          <t>Old entries deleted; recent ones kept.</t>
+        </is>
+      </c>
+      <c r="J171" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K171" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="12" t="inlineStr">
+        <is>
+          <t>RM-01</t>
+        </is>
+      </c>
+      <c r="B172" s="12" t="inlineStr">
+        <is>
+          <t>Player Removal</t>
+        </is>
+      </c>
+      <c r="C172" s="12" t="inlineStr">
+        <is>
+          <t>Removal purges the whole event in one batch</t>
+        </is>
+      </c>
+      <c r="D172" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E172" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F172" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G172" s="12" t="inlineStr">
+        <is>
+          <t>A player seated in a group with match docs, registered in event_participants</t>
+        </is>
+      </c>
+      <c r="H172" s="12" t="inlineStr">
+        <is>
+          <t>1. Remove the player. 2. Inspect every match doc in the event, event_participants, and the withdrawn list.</t>
+        </is>
+      </c>
+      <c r="I172" s="12" t="inlineStr">
+        <is>
+          <t>One batch: player stripped from ALL match docs event-wide, event_participants doc deleted, withdrawn list updated. Any surviving match doc would keep reconstructing their name.</t>
+        </is>
+      </c>
+      <c r="J172" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K172" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="12" t="inlineStr">
+        <is>
+          <t>RM-02</t>
+        </is>
+      </c>
+      <c r="B173" s="12" t="inlineStr">
+        <is>
+          <t>Player Removal</t>
+        </is>
+      </c>
+      <c r="C173" s="12" t="inlineStr">
+        <is>
+          <t>Removed player is not re-seated on reload</t>
+        </is>
+      </c>
+      <c r="D173" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E173" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F173" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G173" s="12" t="inlineStr">
+        <is>
+          <t>Immediately after RM-01</t>
+        </is>
+      </c>
+      <c r="H173" s="12" t="inlineStr">
+        <is>
+          <t>1. Reload the page. 2. Wait for the late-joiner effect to run.</t>
+        </is>
+      </c>
+      <c r="I173" s="12" t="inlineStr">
+        <is>
+          <t>Player stays removed. Because the withdrawal shipped in the same batch, the effect never sees 'unplaced but registered' for them.</t>
+        </is>
+      </c>
+      <c r="J173" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K173" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="12" t="inlineStr">
+        <is>
+          <t>RM-03</t>
+        </is>
+      </c>
+      <c r="B174" s="12" t="inlineStr">
+        <is>
+          <t>Player Removal</t>
+        </is>
+      </c>
+      <c r="C174" s="12" t="inlineStr">
+        <is>
+          <t>Cross-draw duplicates are surfaced, never auto-deleted</t>
+        </is>
+      </c>
+      <c r="D174" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E174" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F174" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G174" s="12" t="inlineStr">
+        <is>
+          <t>The same player seated in two draws (staged)</t>
+        </is>
+      </c>
+      <c r="H174" s="12" t="inlineStr">
+        <is>
+          <t>1. Load the page.</t>
+        </is>
+      </c>
+      <c r="I174" s="12" t="inlineStr">
+        <is>
+          <t>No automatic unseating (AUTO_DEDUPE_ENABLED = false). The duplicate is a bug to fix at the source - silent deletion mid-event is the worse failure.</t>
+        </is>
+      </c>
+      <c r="J174" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K174" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="12" t="inlineStr">
+        <is>
+          <t>GA-01</t>
+        </is>
+      </c>
+      <c r="B175" s="12" t="inlineStr">
+        <is>
+          <t>Group Awards</t>
+        </is>
+      </c>
+      <c r="C175" s="12" t="inlineStr">
+        <is>
+          <t>Board Freshness pays on report creation</t>
+        </is>
+      </c>
+      <c r="D175" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E175" s="12" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="F175" s="12" t="inlineStr">
+        <is>
+          <t>/tasks</t>
+        </is>
+      </c>
+      <c r="G175" s="12" t="inlineStr">
+        <is>
+          <t>A qualifying board report</t>
+        </is>
+      </c>
+      <c r="H175" s="12" t="inlineStr">
+        <is>
+          <t>1. Submit the report (it auto-approves on create).</t>
+        </is>
+      </c>
+      <c r="I175" s="12" t="inlineStr">
+        <is>
+          <t>Bonus paid from onDocumentCreated. An update-based trigger would never fire - courts docs are immutable by rules.</t>
+        </is>
+      </c>
+      <c r="J175" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K175" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="12" t="inlineStr">
+        <is>
+          <t>GA-02</t>
+        </is>
+      </c>
+      <c r="B176" s="12" t="inlineStr">
+        <is>
+          <t>Group Awards</t>
+        </is>
+      </c>
+      <c r="C176" s="12" t="inlineStr">
+        <is>
+          <t>Matchday query stays inside its ±36h window</t>
+        </is>
+      </c>
+      <c r="D176" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E176" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F176" s="12" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="G176" s="12" t="inlineStr">
+        <is>
+          <t>Completed matches inside and outside the window</t>
+        </is>
+      </c>
+      <c r="H176" s="12" t="inlineStr">
+        <is>
+          <t>1. Complete a match; observe the Matchday bonus query.</t>
+        </is>
+      </c>
+      <c r="I176" s="12" t="inlineStr">
+        <is>
+          <t>Only matches within ±36h are read - not the league's full history (the old unbounded query was quadratic and timed out).</t>
+        </is>
+      </c>
+      <c r="J176" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K176" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="12" t="inlineStr">
+        <is>
+          <t>GA-03</t>
+        </is>
+      </c>
+      <c r="B177" s="12" t="inlineStr">
+        <is>
+          <t>Group Awards</t>
+        </is>
+      </c>
+      <c r="C177" s="12" t="inlineStr">
+        <is>
+          <t>taskPoints and groupAwards never double-pay</t>
+        </is>
+      </c>
+      <c r="D177" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E177" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F177" s="12" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="G177" s="12" t="inlineStr">
+        <is>
+          <t>A single action that both engines observe (e.g. court visit)</t>
+        </is>
+      </c>
+      <c r="H177" s="12" t="inlineStr">
+        <is>
+          <t>1. Trigger it once. 2. Sum all point writes.</t>
+        </is>
+      </c>
+      <c r="I177" s="12" t="inlineStr">
+        <is>
+          <t>Per-player tier points (taskPoints.js) and collective bonuses (groupAwards.js) are distinct amounts into distinct fields - no overlap for the same action.</t>
+        </is>
+      </c>
+      <c r="J177" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K177" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="12" t="inlineStr">
+        <is>
+          <t>DR-01</t>
+        </is>
+      </c>
+      <c r="B178" s="12" t="inlineStr">
+        <is>
+          <t>RR Drafts</t>
+        </is>
+      </c>
+      <c r="C178" s="12" t="inlineStr">
+        <is>
+          <t>Draft writes currently fail silently (known bug)</t>
+        </is>
+      </c>
+      <c r="D178" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E178" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F178" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G178" s="12" t="inlineStr">
+        <is>
+          <t>RR draw in preview; repo rules deployed as-is</t>
+        </is>
+      </c>
+      <c r="H178" s="12" t="inlineStr">
+        <is>
+          <t>1. Edit pre-generation groups / withdraw a player. 2. Reload.</t>
+        </is>
+      </c>
+      <c r="I178" s="12" t="inlineStr">
+        <is>
+          <t>EXPECTED FAIL today: the write to events/{id}/rr_drafts/{drawKey} is denied (rules only declare top-level /rr_drafts) and onSnapshot's error path nulls the draft - edits vanish on reload. This case documents the bug; keep it red until the nested rule ships.</t>
+        </is>
+      </c>
+      <c r="J178" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K178" s="12" t="inlineStr">
+        <is>
+          <t>Known bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="12" t="inlineStr">
+        <is>
+          <t>DR-02</t>
+        </is>
+      </c>
+      <c r="B179" s="12" t="inlineStr">
+        <is>
+          <t>RR Drafts</t>
+        </is>
+      </c>
+      <c r="C179" s="12" t="inlineStr">
+        <is>
+          <t>Draft edits persist after the rules fix</t>
+        </is>
+      </c>
+      <c r="D179" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E179" s="12" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="F179" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G179" s="12" t="inlineStr">
+        <is>
+          <t>Nested match /events/{eventId}/rr_drafts/{drawKey} rule deployed</t>
+        </is>
+      </c>
+      <c r="H179" s="12" t="inlineStr">
+        <is>
+          <t>1. Repeat DR-01. 2. Also verify a non-creator's draft write is denied.</t>
+        </is>
+      </c>
+      <c r="I179" s="12" t="inlineStr">
+        <is>
+          <t>Edits persist across reload; creator-only writes enforced via isCreatorOfEvent(eventId). Flip DR-01 to pass.</t>
+        </is>
+      </c>
+      <c r="J179" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K179" s="12" t="inlineStr">
+        <is>
+          <t>Blocked on fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="12" t="inlineStr">
+        <is>
+          <t>VS-01</t>
+        </is>
+      </c>
+      <c r="B180" s="12" t="inlineStr">
+        <is>
+          <t>Draw Visibility</t>
+        </is>
+      </c>
+      <c r="C180" s="12" t="inlineStr">
+        <is>
+          <t>Participant sees the draw they are actually placed in</t>
+        </is>
+      </c>
+      <c r="D180" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E180" s="12" t="inlineStr">
+        <is>
+          <t>Participant</t>
+        </is>
+      </c>
+      <c r="F180" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G180" s="12" t="inlineStr">
+        <is>
+          <t>Creator moved a player Challengers → Masters WITHOUT editing their event_participants skill</t>
+        </is>
+      </c>
+      <c r="H180" s="12" t="inlineStr">
+        <is>
+          <t>1. Sign in as the moved player.</t>
+        </is>
+      </c>
+      <c r="I180" s="12" t="inlineStr">
+        <is>
+          <t>They see the Masters draw (userDraw scans generated matches for their uid). Skill-derived routing would show the wrong draw - do not reintroduce it.</t>
+        </is>
+      </c>
+      <c r="J180" s="12" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="K180" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="12" t="inlineStr">
+        <is>
+          <t>VS-02</t>
+        </is>
+      </c>
+      <c r="B181" s="12" t="inlineStr">
+        <is>
+          <t>Draw Visibility</t>
+        </is>
+      </c>
+      <c r="C181" s="12" t="inlineStr">
+        <is>
+          <t>Pre-generation shows every draw</t>
+        </is>
+      </c>
+      <c r="D181" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E181" s="12" t="inlineStr">
+        <is>
+          <t>Participant</t>
+        </is>
+      </c>
+      <c r="F181" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G181" s="12" t="inlineStr">
+        <is>
+          <t>Registered participant, no draw generated</t>
+        </is>
+      </c>
+      <c r="H181" s="12" t="inlineStr">
+        <is>
+          <t>1. Open the event.</t>
+        </is>
+      </c>
+      <c r="I181" s="12" t="inlineStr">
+        <is>
+          <t>All draws visible (userDraw is deliberately undefined pre-generation - nothing to hide). Do not 'fix' by guessing from skill_level.</t>
+        </is>
+      </c>
+      <c r="J181" s="12" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="K181" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="12" t="inlineStr">
+        <is>
+          <t>VS-03</t>
+        </is>
+      </c>
+      <c r="B182" s="12" t="inlineStr">
+        <is>
+          <t>Draw Visibility</t>
+        </is>
+      </c>
+      <c r="C182" s="12" t="inlineStr">
+        <is>
+          <t>RR participant sees both skill draws, read-only</t>
+        </is>
+      </c>
+      <c r="D182" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E182" s="12" t="inlineStr">
+        <is>
+          <t>Participant</t>
+        </is>
+      </c>
+      <c r="F182" s="12" t="inlineStr">
+        <is>
+          <t>/tournament</t>
+        </is>
+      </c>
+      <c r="G182" s="12" t="inlineStr">
+        <is>
+          <t>RR event with Challengers + Masters draws in the participant's division</t>
+        </is>
+      </c>
+      <c r="H182" s="12" t="inlineStr">
+        <is>
+          <t>1. Open the event as a participant. 2. Attempt any edit affordance.</t>
+        </is>
+      </c>
+      <c r="I182" s="12" t="inlineStr">
+        <is>
+          <t>Both draws of their own division visible, read-only. Creators see all draws.</t>
+        </is>
+      </c>
+      <c r="J182" s="12" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="K182" s="12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:K182"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5751,7 +10905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5851,13 +11005,143 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08 audit pass</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Zones (2026-08-12 rev 3)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Round Robin (2026-08-12 rev 3)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RR Late Joiners (2026-08-12 rev 3)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Points &amp; Stats (2026-08-12 rev 3)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ladder &amp; Friendlies (2026-08-12 rev 3)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Rewards &amp; Services (2026-08-12 rev 3)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Marketplace &amp; Contacts (2026-08-12 rev 3)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Notifications (2026-08-12 rev 3)</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Player Removal (2026-08-12 rev 3)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Group Awards (2026-08-12 rev 3)</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>RR Drafts (2026-08-12 rev 3)</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Draw Visibility (2026-08-12 rev 3)</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
-        <v>91</v>
+      <c r="B23" s="13" t="n">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
